--- a/DCA-Agent-Coverage.xlsx
+++ b/DCA-Agent-Coverage.xlsx
@@ -9,18 +9,19 @@
     <sheet sheetId="3" name="⚡ Generation" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="💥 Impact Analysis" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="🧪 Test Coverage" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="🛡️ Sonar Scan" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="221">
   <si>
     <t>BMAD DCA — AI Agent Coverage</t>
   </si>
   <si>
-    <t>Multi-agent code intelligence suite for the Adobe / Java middleware stack  ·  status as of 2026-07-10  ·  branch feature/aem-ams-acs</t>
+    <t>Multi-agent code intelligence suite for the Adobe / Java middleware stack  ·  status as of 2026-07-19  ·  branch feature/aem-ams-acs</t>
   </si>
   <si>
     <t>Agents at a glance</t>
@@ -39,6 +40,9 @@
   </si>
   <si>
     <t>Standard outputs (A/B/C)</t>
+  </si>
+  <si>
+    <t>Tier</t>
   </si>
   <si>
     <t>🔍  Audit</t>
@@ -58,6 +62,9 @@
 C: 🟡 opt-in (--create-branch) on 3 new engines only</t>
   </si>
   <si>
+    <t>Tier 1+2</t>
+  </si>
+  <si>
     <t>⚡  Generation</t>
   </si>
   <si>
@@ -80,6 +87,9 @@
 C: ❌ not wired</t>
   </si>
   <si>
+    <t>Tier 1</t>
+  </si>
+  <si>
     <t>🧪  Test Coverage</t>
   </si>
   <si>
@@ -91,6 +101,20 @@
 C: ❌ not wired</t>
   </si>
   <si>
+    <t>🛡️  Sonar Scan</t>
+  </si>
+  <si>
+    <t>LLM-driven SonarQube-style analysis: Bugs, Vulnerabilities, Security Hotspots, Code Smells, Duplications, Complexity. Reliability/Security/Maintainability ratings (A–E) + Quality Gate. Dedicated Vulnerabilities Excel sheet with color-coded severity and concrete recommended fixes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A: ✅ (ingest step)
+B: ✅ (ingest step)
+C: 🟡 opt-in (--create-branch)</t>
+  </si>
+  <si>
+    <t>LLM only</t>
+  </si>
+  <si>
     <t>Coverage matrix  —  stack × agent</t>
   </si>
   <si>
@@ -109,6 +133,9 @@
     <t>🧪 Test Coverage</t>
   </si>
   <si>
+    <t>🛡️ Sonar Scan</t>
+  </si>
+  <si>
     <t>AEMaaCS</t>
   </si>
   <si>
@@ -181,11 +208,12 @@
     <t>Headline</t>
   </si>
   <si>
-    <t xml:space="preserve">• All 4 agents now cover all 9 company tech stacks — 36 of 36 stack×agent cells are Done.
+    <t xml:space="preserve">• All 5 agents now cover all 9 company tech stacks — 45 of 45 stack×agent cells are Done.
 • Audit: every stack emits one identical standardized report + CHANGE-LOG (incl. App Builder + Commerce-SaaS eventing/webhook signatures).
 • Generation: deterministic scaffolders for every stack — generated PHP passes php -l, Java is javac-valid — plus LLM/MCP packs.
 • Impact: a Proofhub bug export or a BRD is traced to impacted code with reverse-dependency blast radius on the Input Traceability sheet.
-• Test Coverage: gap analysis across every stack. Full coverage of the company tech stack achieved.</t>
+• Test Coverage: gap analysis across every stack. Full coverage of the company tech stack achieved.
+• Sonar Scan (NEW): LLM-driven SonarQube-style analysis across all 9 stacks. Bugs, Vulnerabilities, Security Hotspots, Code Smells, Duplications, Complexity. Reliability/Security/Maintainability ratings (A–E) + Quality Gate. Dedicated Vulnerabilities Excel sheet with color-coded severity rows and concrete recommended fixes.</t>
   </si>
   <si>
     <t>🔍  Audit Agent — Coverage Detail</t>
@@ -570,6 +598,102 @@
   </si>
   <si>
     <t>•  Class-name matching is package-insensitive; same-named classes across packages can collide.</t>
+  </si>
+  <si>
+    <t>🛡️  Sonar Scan Agent — Coverage Detail</t>
+  </si>
+  <si>
+    <t>✅ (ingest step)</t>
+  </si>
+  <si>
+    <t>🟡 opt-in (--create-branch)</t>
+  </si>
+  <si>
+    <t>Step 1 (LLM) writes sonar-findings.json; Step 2 (--ingest) emits standardized xlsx + CHANGE-LOG + Vulnerabilities sheet.</t>
+  </si>
+  <si>
+    <t>rule-packs/aem/rules.md + scripts/sonar/ingest.ts</t>
+  </si>
+  <si>
+    <t>Bugs (NPE/resource-leak), Vulnerabilities (JCR-SQL2 injection, hardcoded credentials, XSS), Code Smells (S3776 complexity, S1192 dup literals), Duplication, Complexity</t>
+  </si>
+  <si>
+    <t>LLM Tier-2; ratings A–E; Quality Gate; dedicated Vulnerabilities sheet</t>
+  </si>
+  <si>
+    <t>rule-packs/aem/rules.md (shared)</t>
+  </si>
+  <si>
+    <t>Same Java rule pack as AEMaaCS; aemams alias resolves to aem profile</t>
+  </si>
+  <si>
+    <t>Shared rule pack via alias</t>
+  </si>
+  <si>
+    <t>rule-packs/commerce-paas/rules.md + scripts/sonar/ingest.ts</t>
+  </si>
+  <si>
+    <t>PHP: S3649 SQL injection, S2068 hardcoded credentials, S5131 XSS (Block output), S1313 CSRF, S3776 complexity, S1192 dup literals, S1066 collapsible-if</t>
+  </si>
+  <si>
+    <t>LLM Tier-2; Vulnerabilities sheet highlights CRITICAL rows</t>
+  </si>
+  <si>
+    <t>rule-packs/commerce-saas/rules.md + scripts/sonar/ingest.ts</t>
+  </si>
+  <si>
+    <t>JS: S5131 DOM XSS via innerHTML, S2068 hardcoded API keys, S4502 prototype pollution, S2259 null/undefined chain, S1481 unused locals, S125 commented-out code</t>
+  </si>
+  <si>
+    <t>LLM Tier-2</t>
+  </si>
+  <si>
+    <t>rule-packs/app-builder/rules.md + scripts/sonar/ingest.ts</t>
+  </si>
+  <si>
+    <t>Node.js: S5131 SSRF via user-supplied URL, S2068 hardcoded Adobe IO/Commerce credentials, S4502 unvalidated event payload injection, S4507 unrestricted action, S3776 complexity</t>
+  </si>
+  <si>
+    <t>rule-packs/sling/rules.md + scripts/sonar/ingest.ts</t>
+  </si>
+  <si>
+    <t>Java: S2259 NPE on resource chains, S2095 unclosed ResourceResolver/Session, S2068 hardcoded credentials, S3649 JCR-SQL2 injection, S5131 Sling Servlet XSS, S3776 complexity</t>
+  </si>
+  <si>
+    <t>rule-packs/spring/rules.md + scripts/sonar/ingest.ts</t>
+  </si>
+  <si>
+    <t>Java: S3649 SQL injection, S2068 hardcoded secrets (@Value defaults), S5131 XSS, S4719 Spring Security misconfiguration, S2259 Optional.get() NPE, S2095 unclosed resources</t>
+  </si>
+  <si>
+    <t>LLM Tier-2; fixture verified: CRITICAL SQL injection → Gate FAIL</t>
+  </si>
+  <si>
+    <t>rule-packs/eds/rules.md + scripts/sonar/ingest.ts</t>
+  </si>
+  <si>
+    <t>JS: S5131 DOM XSS (innerHTML), S2068 hardcoded API endpoints, S2259 unchecked DOM query results, S1481 unused locals, S125 commented-out code, S3776 complexity</t>
+  </si>
+  <si>
+    <t>rule-packs/eds-commerce/rules.md + scripts/sonar/ingest.ts</t>
+  </si>
+  <si>
+    <t>JS: S5131 DOM XSS via commerce product HTML, S2068 hardcoded Commerce API key, S4502 cart mutation with unvalidated SKU, S3776 complexity. Extends EDS rule pack.</t>
+  </si>
+  <si>
+    <t>•  LLM-only (no deterministic scanner) — findings quality depends on context window fit and LLM reasoning accuracy.</t>
+  </si>
+  <si>
+    <t>•  Real SonarQube/SonarCloud API ingestion (--sonar-host-url, fetching issues from a server) is out of scope for v1.</t>
+  </si>
+  <si>
+    <t>•  Coverage-based Quality Gate conditions (new-code gate, coverage %) are not supported — covered by the Test-Coverage agent.</t>
+  </si>
+  <si>
+    <t>•  Recommendation concreteness (the primary deliverable) is enforced by SKILL.md authoring rules, not by code schema validation.</t>
+  </si>
+  <si>
+    <t>•  Standard branch cut (output C) is opt-in via --create-branch; not auto-wired.</t>
   </si>
 </sst>
 </file>
@@ -729,13 +853,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1089,14 +1213,14 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="5" width="26" customWidth="1"/>
+    <col min="2" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1104,8 +1228,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1113,8 +1238,9 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="2"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1122,8 +1248,9 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -1139,379 +1266,471 @@
       <c r="E5" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" ht="54" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" ht="54" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="7" t="s">
+    </row>
+    <row r="8" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>10</v>
-      </c>
       <c r="D8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>10</v>
-      </c>
       <c r="D9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="D10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="9" t="s">
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="B13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="C13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="D13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="E13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="F13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="B14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="B15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B16" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="B17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="B18" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="B19" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="6" t="s">
+      <c r="B20" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="7">
-        <v>36</v>
-      </c>
-      <c r="D25" s="10" t="s">
+      <c r="B21" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="B22" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>37</v>
+      </c>
       <c r="B26" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C26" s="7">
-        <v>0</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C27" s="7">
         <v>0</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>48</v>
+      <c r="D27" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
+      <c r="F27" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="7">
+        <v>0</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>60</v>
+      </c>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="13"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="13"/>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="13"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A30:E33"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:F35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1535,7 +1754,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1544,7 +1763,7 @@
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1553,7 +1772,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1562,39 +1781,39 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>60</v>
+      <c r="A6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1603,177 +1822,177 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>29</v>
+      <c r="A10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>29</v>
+      <c r="A11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>29</v>
+      <c r="A12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>29</v>
+      <c r="A13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>29</v>
+      <c r="A14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>29</v>
+      <c r="A15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>29</v>
+      <c r="A16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>29</v>
+      <c r="A17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>29</v>
+      <c r="A18" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1782,7 +2001,7 @@
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1791,7 +2010,7 @@
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -1800,7 +2019,7 @@
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -1809,7 +2028,7 @@
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -1851,7 +2070,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1860,7 +2079,7 @@
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1869,7 +2088,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1878,39 +2097,39 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>102</v>
+      <c r="A6" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1919,177 +2138,177 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>29</v>
+      <c r="A10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>29</v>
+      <c r="B16" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>29</v>
+      <c r="A17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>29</v>
+      <c r="A18" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -2098,7 +2317,7 @@
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -2107,7 +2326,7 @@
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -2116,7 +2335,7 @@
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -2157,7 +2376,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2166,7 +2385,7 @@
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2175,7 +2394,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2184,39 +2403,39 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>102</v>
+      <c r="A6" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -2225,177 +2444,177 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>29</v>
+      <c r="A10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>29</v>
+      <c r="A11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>29</v>
+      <c r="A12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>29</v>
+      <c r="A13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>29</v>
+      <c r="A14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E14" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="15" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>29</v>
+      <c r="B16" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>29</v>
+      <c r="A17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>29</v>
+      <c r="A18" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -2404,7 +2623,7 @@
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -2413,7 +2632,7 @@
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -2422,7 +2641,7 @@
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -2431,7 +2650,7 @@
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -2440,7 +2659,7 @@
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -2483,7 +2702,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2492,7 +2711,7 @@
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2501,7 +2720,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2510,39 +2729,39 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>102</v>
+      <c r="A6" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -2551,177 +2770,177 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>29</v>
+      <c r="A10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>29</v>
+      <c r="B16" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>29</v>
+      <c r="A17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>29</v>
+      <c r="A18" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -2730,7 +2949,7 @@
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -2739,7 +2958,7 @@
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -2748,7 +2967,7 @@
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -2757,7 +2976,7 @@
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -2780,4 +2999,330 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF2E75B6"/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="52" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>